--- a/光伏支架_3D3S导入_测试.xlsx
+++ b/光伏支架_3D3S导入_测试.xlsx
@@ -1470,12 +1470,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>冷弯薄壁C型钢</t>
+          <t>冷弯C型钢</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>C110×70×50×2.0</t>
+          <t>C110X70X50X2.0</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>L50×5</t>
+          <t>L50x5</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>L50×5</t>
+          <t>L50x5</t>
         </is>
       </c>
     </row>
@@ -1574,12 +1574,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>冷弯薄壁C型钢</t>
+          <t>冷弯C型钢</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>C110×70×50×2.0</t>
+          <t>C110X70X50X2.0</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>L50×5</t>
+          <t>L50x5</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>L50×5</t>
+          <t>L50x5</t>
         </is>
       </c>
     </row>
@@ -1678,12 +1678,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>冷弯薄壁C型钢</t>
+          <t>冷弯C型钢</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>C110×70×50×2.0</t>
+          <t>C110X70X50X2.0</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>L50×5</t>
+          <t>L50x5</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>L50×5</t>
+          <t>L50x5</t>
         </is>
       </c>
     </row>
@@ -1782,12 +1782,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>冷弯薄壁C型钢</t>
+          <t>冷弯C型钢</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>C110×70×50×2.0</t>
+          <t>C110X70X50X2.0</t>
         </is>
       </c>
     </row>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>L50×5</t>
+          <t>L50x5</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>L50×5</t>
+          <t>L50x5</t>
         </is>
       </c>
     </row>
@@ -1886,12 +1886,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>冷弯薄壁C型钢</t>
+          <t>冷弯C型钢</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>C110×70×50×2.0</t>
+          <t>C110X70X50X2.0</t>
         </is>
       </c>
     </row>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>L50×5</t>
+          <t>L50x5</t>
         </is>
       </c>
     </row>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>L50×5</t>
+          <t>L50x5</t>
         </is>
       </c>
     </row>
@@ -1990,12 +1990,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>冷弯薄壁C型钢</t>
+          <t>冷弯C型钢</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>C110×70×50×2.0</t>
+          <t>C110X70X50X2.0</t>
         </is>
       </c>
     </row>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>L50×5</t>
+          <t>L50x5</t>
         </is>
       </c>
     </row>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>L50×5</t>
+          <t>L50x5</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>冷弯薄壁C型钢</t>
+          <t>冷弯C型钢</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>C110×70×50×2.0</t>
+          <t>C110X70X50X2.0</t>
         </is>
       </c>
     </row>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>L50×5</t>
+          <t>L50x5</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>L50×5</t>
+          <t>L50x5</t>
         </is>
       </c>
     </row>
@@ -2198,12 +2198,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>冷弯薄壁C型钢</t>
+          <t>冷弯C型钢</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>C110×70×50×2.0</t>
+          <t>C110X70X50X2.0</t>
         </is>
       </c>
     </row>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>L50×5</t>
+          <t>L50x5</t>
         </is>
       </c>
     </row>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>L50×5</t>
+          <t>L50x5</t>
         </is>
       </c>
     </row>
@@ -2302,12 +2302,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>冷弯薄壁C型钢</t>
+          <t>冷弯C型钢</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>C110×70×50×2.0</t>
+          <t>C110X70X50X2.0</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>L50×5</t>
+          <t>L50x5</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>L50×5</t>
+          <t>L50x5</t>
         </is>
       </c>
     </row>
@@ -2380,12 +2380,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>冷弯薄壁C型钢</t>
+          <t>冷弯C型钢</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>41系列C型钢(41×41)</t>
+          <t>41系列C型钢(41X41)</t>
         </is>
       </c>
     </row>
@@ -2406,12 +2406,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>冷弯薄壁C型钢</t>
+          <t>冷弯C型钢</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>41系列C型钢(41×41)</t>
+          <t>41系列C型钢(41X41)</t>
         </is>
       </c>
     </row>
@@ -2432,12 +2432,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>冷弯薄壁C型钢</t>
+          <t>冷弯C型钢</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>41系列C型钢(41×41)</t>
+          <t>41系列C型钢(41X41)</t>
         </is>
       </c>
     </row>
@@ -2458,12 +2458,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>冷弯薄壁C型钢</t>
+          <t>冷弯C型钢</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>41系列C型钢(41×41)</t>
+          <t>41系列C型钢(41X41)</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>冷弯薄壁C型钢</t>
+          <t>冷弯C型钢</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>C110×70×50×2.0</t>
+          <t>C110X70X50X2.0</t>
         </is>
       </c>
     </row>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>L50×5</t>
+          <t>L50x5</t>
         </is>
       </c>
     </row>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>L50×5</t>
+          <t>L50x5</t>
         </is>
       </c>
     </row>
@@ -2700,12 +2700,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>冷弯薄壁C型钢</t>
+          <t>冷弯C型钢</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>C110×70×50×2.0</t>
+          <t>C110X70X50X2.0</t>
         </is>
       </c>
     </row>
@@ -2743,7 +2743,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>L50×5</t>
+          <t>L50x5</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>L50×5</t>
+          <t>L50x5</t>
         </is>
       </c>
     </row>
@@ -2852,12 +2852,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>冷弯薄壁C型钢</t>
+          <t>冷弯C型钢</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>C110×70×50×2.0</t>
+          <t>C110X70X50X2.0</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>L50×5</t>
+          <t>L50x5</t>
         </is>
       </c>
     </row>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>L50×5</t>
+          <t>L50x5</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>冷弯薄壁C型钢</t>
+          <t>冷弯C型钢</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>C110×70×50×2.0</t>
+          <t>C110X70X50X2.0</t>
         </is>
       </c>
     </row>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>L50×5</t>
+          <t>L50x5</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>L50×5</t>
+          <t>L50x5</t>
         </is>
       </c>
     </row>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>冷弯薄壁C型钢</t>
+          <t>冷弯C型钢</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>C110×70×50×2.0</t>
+          <t>C110X70X50X2.0</t>
         </is>
       </c>
     </row>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>L50×5</t>
+          <t>L50x5</t>
         </is>
       </c>
     </row>
@@ -3237,7 +3237,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>L50×5</t>
+          <t>L50x5</t>
         </is>
       </c>
     </row>
@@ -3308,12 +3308,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>冷弯薄壁C型钢</t>
+          <t>冷弯C型钢</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>C110×70×50×2.0</t>
+          <t>C110X70X50X2.0</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>L50×5</t>
+          <t>L50x5</t>
         </is>
       </c>
     </row>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>L50×5</t>
+          <t>L50x5</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>冷弯薄壁C型钢</t>
+          <t>冷弯C型钢</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>C110×70×50×2.0</t>
+          <t>C110X70X50X2.0</t>
         </is>
       </c>
     </row>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>L50×5</t>
+          <t>L50x5</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>L50×5</t>
+          <t>L50x5</t>
         </is>
       </c>
     </row>
@@ -3612,12 +3612,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>冷弯薄壁C型钢</t>
+          <t>冷弯C型钢</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>C110×70×50×2.0</t>
+          <t>C110X70X50X2.0</t>
         </is>
       </c>
     </row>
@@ -3655,7 +3655,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>L50×5</t>
+          <t>L50x5</t>
         </is>
       </c>
     </row>
@@ -3693,7 +3693,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>L50×5</t>
+          <t>L50x5</t>
         </is>
       </c>
     </row>
@@ -3764,12 +3764,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>冷弯薄壁C型钢</t>
+          <t>冷弯C型钢</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>C110×70×50×2.0</t>
+          <t>C110X70X50X2.0</t>
         </is>
       </c>
     </row>
@@ -3807,7 +3807,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>L50×5</t>
+          <t>L50x5</t>
         </is>
       </c>
     </row>
@@ -3845,7 +3845,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>L50×5</t>
+          <t>L50x5</t>
         </is>
       </c>
     </row>
@@ -3878,12 +3878,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>冷弯薄壁C型钢</t>
+          <t>冷弯C型钢</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>41系列C型钢(41×41)</t>
+          <t>41系列C型钢(41X41)</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>冷弯薄壁C型钢</t>
+          <t>冷弯C型钢</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>41系列C型钢(41×41)</t>
+          <t>41系列C型钢(41X41)</t>
         </is>
       </c>
     </row>
@@ -3954,12 +3954,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>冷弯薄壁C型钢</t>
+          <t>冷弯C型钢</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>41系列C型钢(41×41)</t>
+          <t>41系列C型钢(41X41)</t>
         </is>
       </c>
     </row>
@@ -3992,12 +3992,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>冷弯薄壁C型钢</t>
+          <t>冷弯C型钢</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>41系列C型钢(41×41)</t>
+          <t>41系列C型钢(41X41)</t>
         </is>
       </c>
     </row>

--- a/光伏支架_3D3S导入_测试.xlsx
+++ b/光伏支架_3D3S导入_测试.xlsx
@@ -1470,12 +1470,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>冷弯C型钢</t>
+          <t>冷弯卷边槽钢</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>C110X70X50X2.0</t>
+          <t>C140X50X20X2.5</t>
         </is>
       </c>
     </row>
@@ -1574,12 +1574,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>冷弯C型钢</t>
+          <t>冷弯卷边槽钢</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>C110X70X50X2.0</t>
+          <t>C140X50X20X2.5</t>
         </is>
       </c>
     </row>
@@ -1678,12 +1678,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>冷弯C型钢</t>
+          <t>冷弯卷边槽钢</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>C110X70X50X2.0</t>
+          <t>C140X50X20X2.5</t>
         </is>
       </c>
     </row>
@@ -1782,12 +1782,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>冷弯C型钢</t>
+          <t>冷弯卷边槽钢</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>C110X70X50X2.0</t>
+          <t>C140X50X20X2.5</t>
         </is>
       </c>
     </row>
@@ -1886,12 +1886,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>冷弯C型钢</t>
+          <t>冷弯卷边槽钢</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>C110X70X50X2.0</t>
+          <t>C140X50X20X2.5</t>
         </is>
       </c>
     </row>
@@ -1990,12 +1990,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>冷弯C型钢</t>
+          <t>冷弯卷边槽钢</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>C110X70X50X2.0</t>
+          <t>C140X50X20X2.5</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>冷弯C型钢</t>
+          <t>冷弯卷边槽钢</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>C110X70X50X2.0</t>
+          <t>C140X50X20X2.5</t>
         </is>
       </c>
     </row>
@@ -2198,12 +2198,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>冷弯C型钢</t>
+          <t>冷弯卷边槽钢</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>C110X70X50X2.0</t>
+          <t>C140X50X20X2.5</t>
         </is>
       </c>
     </row>
@@ -2302,12 +2302,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>冷弯C型钢</t>
+          <t>冷弯卷边槽钢</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>C110X70X50X2.0</t>
+          <t>C140X50X20X2.5</t>
         </is>
       </c>
     </row>
@@ -2380,12 +2380,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>冷弯C型钢</t>
+          <t>冷弯卷边槽钢</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>41系列C型钢(41X41)</t>
+          <t>C100X50X15X2.5</t>
         </is>
       </c>
     </row>
@@ -2406,12 +2406,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>冷弯C型钢</t>
+          <t>冷弯卷边槽钢</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>41系列C型钢(41X41)</t>
+          <t>C100X50X15X2.5</t>
         </is>
       </c>
     </row>
@@ -2432,12 +2432,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>冷弯C型钢</t>
+          <t>冷弯卷边槽钢</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>41系列C型钢(41X41)</t>
+          <t>C100X50X15X2.5</t>
         </is>
       </c>
     </row>
@@ -2458,12 +2458,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>冷弯C型钢</t>
+          <t>冷弯卷边槽钢</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>41系列C型钢(41X41)</t>
+          <t>C100X50X15X2.5</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>冷弯C型钢</t>
+          <t>冷弯卷边槽钢</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>C110X70X50X2.0</t>
+          <t>C140X50X20X2.5</t>
         </is>
       </c>
     </row>
@@ -2700,12 +2700,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>冷弯C型钢</t>
+          <t>冷弯卷边槽钢</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>C110X70X50X2.0</t>
+          <t>C140X50X20X2.5</t>
         </is>
       </c>
     </row>
@@ -2852,12 +2852,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>冷弯C型钢</t>
+          <t>冷弯卷边槽钢</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>C110X70X50X2.0</t>
+          <t>C140X50X20X2.5</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>冷弯C型钢</t>
+          <t>冷弯卷边槽钢</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>C110X70X50X2.0</t>
+          <t>C140X50X20X2.5</t>
         </is>
       </c>
     </row>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>冷弯C型钢</t>
+          <t>冷弯卷边槽钢</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>C110X70X50X2.0</t>
+          <t>C140X50X20X2.5</t>
         </is>
       </c>
     </row>
@@ -3308,12 +3308,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>冷弯C型钢</t>
+          <t>冷弯卷边槽钢</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>C110X70X50X2.0</t>
+          <t>C140X50X20X2.5</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>冷弯C型钢</t>
+          <t>冷弯卷边槽钢</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>C110X70X50X2.0</t>
+          <t>C140X50X20X2.5</t>
         </is>
       </c>
     </row>
@@ -3612,12 +3612,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>冷弯C型钢</t>
+          <t>冷弯卷边槽钢</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>C110X70X50X2.0</t>
+          <t>C140X50X20X2.5</t>
         </is>
       </c>
     </row>
@@ -3764,12 +3764,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>冷弯C型钢</t>
+          <t>冷弯卷边槽钢</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>C110X70X50X2.0</t>
+          <t>C140X50X20X2.5</t>
         </is>
       </c>
     </row>
@@ -3878,12 +3878,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>冷弯C型钢</t>
+          <t>冷弯卷边槽钢</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>41系列C型钢(41X41)</t>
+          <t>C100X50X15X2.5</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>冷弯C型钢</t>
+          <t>冷弯卷边槽钢</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>41系列C型钢(41X41)</t>
+          <t>C100X50X15X2.5</t>
         </is>
       </c>
     </row>
@@ -3954,12 +3954,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>冷弯C型钢</t>
+          <t>冷弯卷边槽钢</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>41系列C型钢(41X41)</t>
+          <t>C100X50X15X2.5</t>
         </is>
       </c>
     </row>
@@ -3992,12 +3992,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>冷弯C型钢</t>
+          <t>冷弯卷边槽钢</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>41系列C型钢(41X41)</t>
+          <t>C100X50X15X2.5</t>
         </is>
       </c>
     </row>

--- a/光伏支架_3D3S导入_测试.xlsx
+++ b/光伏支架_3D3S导入_测试.xlsx
@@ -1449,7 +1449,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>槽8</t>
+          <t>[8</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>槽8</t>
+          <t>[8</t>
         </is>
       </c>
     </row>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>槽8</t>
+          <t>[8</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>槽8</t>
+          <t>[8</t>
         </is>
       </c>
     </row>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>槽8</t>
+          <t>[8</t>
         </is>
       </c>
     </row>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>槽8</t>
+          <t>[8</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>槽8</t>
+          <t>[8</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>槽8</t>
+          <t>[8</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>槽8</t>
+          <t>[8</t>
         </is>
       </c>
     </row>
@@ -2515,7 +2515,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>槽8</t>
+          <t>[8</t>
         </is>
       </c>
     </row>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>槽8</t>
+          <t>[8</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>槽8</t>
+          <t>[8</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>槽8</t>
+          <t>[8</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>槽8</t>
+          <t>[8</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>槽8</t>
+          <t>[8</t>
         </is>
       </c>
     </row>
@@ -3427,7 +3427,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>槽8</t>
+          <t>[8</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>槽8</t>
+          <t>[8</t>
         </is>
       </c>
     </row>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>槽8</t>
+          <t>[8</t>
         </is>
       </c>
     </row>
